--- a/forecast_app_final/data/shift_avail.xlsx
+++ b/forecast_app_final/data/shift_avail.xlsx
@@ -429,10 +429,10 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>689</v>
+        <v>91</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>42</v>
@@ -443,10 +443,10 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>652</v>
+        <v>137</v>
       </c>
       <c r="C3">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -457,10 +457,10 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>528</v>
+        <v>181</v>
       </c>
       <c r="C4">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -471,10 +471,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>481</v>
+        <v>188</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>62</v>
@@ -485,10 +485,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>404</v>
+        <v>198</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -499,10 +499,10 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>372</v>
+        <v>166</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>53</v>
@@ -513,10 +513,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>495</v>
+        <v>114</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -527,10 +527,10 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>598</v>
+        <v>75</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>37</v>
